--- a/Wikidata Delta/uz_gen_excels/pep_uzbekistan_living_relevant_rca_lookup.xlsx
+++ b/Wikidata Delta/uz_gen_excels/pep_uzbekistan_living_relevant_rca_lookup.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UZ-GEN-LK-SO4AK-RCA-1</t>
+          <t>UZ-GEN-LK-1HSLO-RCA-1</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UZ-GEN-TK-67MWV-RCA-1</t>
+          <t>UZ-GEN-TK-BEU9O-RCA-1</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UZ-GEN-ZM-AJQOP-RCA-1</t>
+          <t>UZ-GEN-ZM-WRJX2-RCA-1</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UZ-GEN-TT-AGHDO-RCA-1</t>
+          <t>UZ-GEN-TT-3U988-RCA-1</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UZ-GEN-LKT-E761N-RCA-1</t>
+          <t>UZ-GEN-LKT-7C98Z-RCA-1</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UZ-GEN-SM-QZY37-RCA-1</t>
+          <t>UZ-GEN-SM-04LJS-RCA-1</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UZ-GEN-IH-6G5P2-RCA-1</t>
+          <t>UZ-GEN-IH-0IVDH-RCA-1</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UZ-GEN-IK-2A3V8-RCA-1</t>
+          <t>UZ-GEN-IK-5A8DA-RCA-1</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UZ-GEN-OT-Y6OMQ-RCA-1</t>
+          <t>UZ-GEN-OT-WQLUE-RCA-1</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UZ-GEN-NU-DE5TE-RCA-1</t>
+          <t>UZ-GEN-NU-7FW1K-RCA-1</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UZ-GEN-IP-W3VCD-RCA-1</t>
+          <t>UZ-GEN-IP-4LXIG-RCA-1</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UZ-GEN-VPJ-KXHV0-RCA-1</t>
+          <t>UZ-GEN-VPJ-C1JFM-RCA-1</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UZ-GEN-GK-UYW9Q-RCA-1</t>
+          <t>UZ-GEN-GK-75XA0-RCA-1</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UZ-GEN-SM-H3YI1-RCA-1</t>
+          <t>UZ-GEN-SM-94271-RCA-1</t>
         </is>
       </c>
     </row>
